--- a/audit/qa-integral-dataset/fixtures/QA_cutover_grandparent.xlsx
+++ b/audit/qa-integral-dataset/fixtures/QA_cutover_grandparent.xlsx
@@ -1908,7 +1908,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-10-18T01:14:59.096477+00:00</t>
+          <t>2026-10-18T03:03:40.418706+00:00</t>
         </is>
       </c>
     </row>

--- a/audit/qa-integral-dataset/fixtures/QA_cutover_grandparent.xlsx
+++ b/audit/qa-integral-dataset/fixtures/QA_cutover_grandparent.xlsx
@@ -1908,7 +1908,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-10-18T03:03:40.418706+00:00</t>
+          <t>2026-10-23T10:13:29.907314+00:00</t>
         </is>
       </c>
     </row>
@@ -2116,7 +2116,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>2026-03-22</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -2193,7 +2193,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="L3" t="n">
@@ -2234,7 +2234,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E1"/>
+  <dimension ref="A1:F1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2263,6 +2263,11 @@
           <t>parent_code</t>
         </is>
       </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>source</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
